--- a/Project_ETF/ETF_Investment_Portfolio/009805/ETF_Investment_Portfolio_20260813.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/009805/ETF_Investment_Portfolio_20260813.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D71"/>
+  <dimension ref="A1:D72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24.75" customWidth="1" min="1" max="1"/>
@@ -611,12 +611,12 @@
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>76,207</t>
+          <t>75,607</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>11.47%</t>
+          <t>11.32%</t>
         </is>
       </c>
     </row>
@@ -633,12 +633,12 @@
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>31,596</t>
+          <t>31,296</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>10.75%</t>
+          <t>10.85%</t>
         </is>
       </c>
     </row>
@@ -655,12 +655,12 @@
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>88,425</t>
+          <t>87,625</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>8.34%</t>
+          <t>8.31%</t>
         </is>
       </c>
     </row>
@@ -677,12 +677,12 @@
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>34,755</t>
+          <t>34,455</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>7.71%</t>
+          <t>7.66%</t>
         </is>
       </c>
     </row>
@@ -699,12 +699,12 @@
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>191,056</t>
+          <t>189,256</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>5.36%</t>
+          <t>5.38%</t>
         </is>
       </c>
     </row>
@@ -721,12 +721,12 @@
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>101,591</t>
+          <t>100,691</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>4.10%</t>
+          <t>4.14%</t>
         </is>
       </c>
     </row>
@@ -743,12 +743,12 @@
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>47,895</t>
+          <t>47,495</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>3.72%</t>
+          <t>3.71%</t>
         </is>
       </c>
     </row>
@@ -765,12 +765,12 @@
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>110,166</t>
+          <t>109,166</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>3.33%</t>
+          <t>3.35%</t>
         </is>
       </c>
     </row>
@@ -787,12 +787,12 @@
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>57,659</t>
+          <t>57,159</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>3.23%</t>
+          <t>3.21%</t>
         </is>
       </c>
     </row>
@@ -809,12 +809,12 @@
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>18,979</t>
+          <t>18,779</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>3.18%</t>
+          <t>3.14%</t>
         </is>
       </c>
     </row>
@@ -831,12 +831,12 @@
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>114,583</t>
+          <t>113,583</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>2.55%</t>
+          <t>2.57%</t>
         </is>
       </c>
     </row>
@@ -853,12 +853,12 @@
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>53,027</t>
+          <t>52,627</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>2.16%</t>
+          <t>2.18%</t>
         </is>
       </c>
     </row>
@@ -875,7 +875,7 @@
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>22,031</t>
+          <t>21,831</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
@@ -897,12 +897,12 @@
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>133,501</t>
+          <t>132,201</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>1.97%</t>
+          <t>1.99%</t>
         </is>
       </c>
     </row>
@@ -919,12 +919,12 @@
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>23,804</t>
+          <t>23,604</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>1.77%</t>
+          <t>1.74%</t>
         </is>
       </c>
     </row>
@@ -941,12 +941,12 @@
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>61,003</t>
+          <t>60,403</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>1.57%</t>
+          <t>1.58%</t>
         </is>
       </c>
     </row>
@@ -963,12 +963,12 @@
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>35,980</t>
+          <t>35,680</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>1.27%</t>
+          <t>1.28%</t>
         </is>
       </c>
     </row>
@@ -985,7 +985,7 @@
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>48,636</t>
+          <t>48,236</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
@@ -1007,7 +1007,7 @@
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>75,401</t>
+          <t>74,701</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
@@ -1019,44 +1019,44 @@
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>ES US</t>
+          <t>EIX US</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>Eversource能源</t>
+          <t>愛迪生國際</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>48,960</t>
+          <t>49,710</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>1.15%</t>
+          <t>1.16%</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>EIX US</t>
+          <t>ES US</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>愛迪生國際</t>
+          <t>Eversource能源</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>50,110</t>
+          <t>48,560</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>1.14%</t>
+          <t>1.16%</t>
         </is>
       </c>
     </row>
@@ -1073,12 +1073,12 @@
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>31,810</t>
+          <t>31,510</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>1.14%</t>
+          <t>1.15%</t>
         </is>
       </c>
     </row>
@@ -1095,51 +1095,51 @@
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>93,063</t>
+          <t>92,163</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>1.08%</t>
+          <t>1.11%</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>ETR US</t>
+          <t>VST US</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>安特吉公司</t>
+          <t>維斯達能源公司</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>29,745</t>
+          <t>21,558</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>1.05%</t>
+          <t>1.04%</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>VST US</t>
+          <t>ETR US</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>維斯達能源公司</t>
+          <t>安特吉公司</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>21,758</t>
+          <t>29,545</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
@@ -1166,29 +1166,29 @@
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>1.01%</t>
+          <t>1.04%</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>AEIS US</t>
+          <t>ACM UN</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>艾儀有限公司</t>
+          <t>艾奕康</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>8,804</t>
+          <t>45,627</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>0.97%</t>
+          <t>0.96%</t>
         </is>
       </c>
     </row>
@@ -1205,7 +1205,7 @@
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>26,969</t>
+          <t>26,769</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
@@ -1217,22 +1217,22 @@
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>ACM UN</t>
+          <t>AEIS US</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>艾奕康</t>
+          <t>艾儀有限公司</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>46,027</t>
+          <t>8,704</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>0.92%</t>
+          <t>0.95%</t>
         </is>
       </c>
     </row>
@@ -1249,12 +1249,12 @@
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>20,209</t>
+          <t>20,109</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>0.92%</t>
+          <t>0.93%</t>
         </is>
       </c>
     </row>
@@ -1276,7 +1276,7 @@
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>0.90%</t>
+          <t>0.89%</t>
         </is>
       </c>
     </row>
@@ -1293,78 +1293,78 @@
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>73,474</t>
+          <t>72,774</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>0.85%</t>
+          <t>0.86%</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>PCG US</t>
+          <t>ENS US</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>太平洋電力瓦斯公司</t>
+          <t>EnerSys</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>142,945</t>
+          <t>12,852</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t>0.81%</t>
+          <t>0.84%</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>EVRG US</t>
+          <t>PCG US</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>Evergy公司</t>
+          <t>太平洋電力瓦斯公司</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>29,614</t>
+          <t>141,545</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
         <is>
-          <t>0.81%</t>
+          <t>0.82%</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>ENS US</t>
+          <t>EVRG US</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>EnerSys</t>
+          <t>Evergy公司</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>12,952</t>
+          <t>29,414</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t>0.79%</t>
+          <t>0.81%</t>
         </is>
       </c>
     </row>
@@ -1386,7 +1386,7 @@
       </c>
       <c r="D56" s="4" t="inlineStr">
         <is>
-          <t>0.76%</t>
+          <t>0.78%</t>
         </is>
       </c>
     </row>
@@ -1408,7 +1408,7 @@
       </c>
       <c r="D57" s="4" t="inlineStr">
         <is>
-          <t>0.75%</t>
+          <t>0.74%</t>
         </is>
       </c>
     </row>
@@ -1425,7 +1425,7 @@
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>29,991</t>
+          <t>29,791</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr">
@@ -1447,7 +1447,7 @@
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>25,181</t>
+          <t>24,981</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
@@ -1469,7 +1469,7 @@
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>42,583</t>
+          <t>42,183</t>
         </is>
       </c>
       <c r="D60" s="4" t="inlineStr">
@@ -1481,17 +1481,17 @@
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>NRG US</t>
+          <t>PNW US</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>NRG Energy Inc</t>
+          <t>皮那可資本公司</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>13,124</t>
+          <t>15,627</t>
         </is>
       </c>
       <c r="D61" s="4" t="inlineStr">
@@ -1503,17 +1503,17 @@
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>PNW US</t>
+          <t>NRG US</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>皮那可資本公司</t>
+          <t>NRG Energy Inc</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>15,727</t>
+          <t>13,024</t>
         </is>
       </c>
       <c r="D62" s="4" t="inlineStr">
@@ -1525,17 +1525,17 @@
     <row r="63">
       <c r="A63" s="3" t="inlineStr">
         <is>
-          <t>POWL US</t>
+          <t>AES US</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>Powell工業公司</t>
+          <t>愛伊斯公司</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>6,627</t>
+          <t>91,602</t>
         </is>
       </c>
       <c r="D63" s="4" t="inlineStr">
@@ -1547,17 +1547,17 @@
     <row r="64">
       <c r="A64" s="3" t="inlineStr">
         <is>
-          <t>AES US</t>
+          <t>POWL US</t>
         </is>
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>愛伊斯公司</t>
+          <t>Powell工業公司</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>92,502</t>
+          <t>6,627</t>
         </is>
       </c>
       <c r="D64" s="4" t="inlineStr">
@@ -1579,7 +1579,7 @@
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>5,778</t>
+          <t>5,678</t>
         </is>
       </c>
       <c r="D65" s="4" t="inlineStr">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="D66" s="4" t="inlineStr">
         <is>
-          <t>0.39%</t>
+          <t>0.38%</t>
         </is>
       </c>
     </row>
@@ -1623,7 +1623,7 @@
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>23,019</t>
+          <t>22,819</t>
         </is>
       </c>
       <c r="D67" s="4" t="inlineStr">
@@ -1635,39 +1635,39 @@
     <row r="68">
       <c r="A68" s="3" t="inlineStr">
         <is>
-          <t>BELFB US</t>
+          <t>ITRI US</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>百富電子有限公司</t>
+          <t>英特隆公司</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
         <is>
-          <t>2,739</t>
+          <t>7,821</t>
         </is>
       </c>
       <c r="D68" s="4" t="inlineStr">
         <is>
-          <t>0.26%</t>
+          <t>0.27%</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="3" t="inlineStr">
         <is>
-          <t>ITRI US</t>
+          <t>BELFB US</t>
         </is>
       </c>
       <c r="B69" s="3" t="inlineStr">
         <is>
-          <t>英特隆公司</t>
+          <t>百富電子有限公司</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
         <is>
-          <t>7,821</t>
+          <t>2,739</t>
         </is>
       </c>
       <c r="D69" s="4" t="inlineStr">
@@ -1689,7 +1689,7 @@
       </c>
       <c r="C70" s="4" t="inlineStr">
         <is>
-          <t>18,053</t>
+          <t>17,853</t>
         </is>
       </c>
       <c r="D70" s="4" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>37,461</t>
+          <t>37,061</t>
         </is>
       </c>
       <c r="D71" s="4" t="inlineStr">
@@ -1719,6 +1719,20 @@
           <t>0.01%</t>
         </is>
       </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="3" t="inlineStr">
+        <is>
+          <t>C_NTD</t>
+        </is>
+      </c>
+      <c r="B72" s="3" t="inlineStr"/>
+      <c r="C72" s="4" t="inlineStr">
+        <is>
+          <t>126,429,093</t>
+        </is>
+      </c>
+      <c r="D72" s="4" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="5">
